--- a/Interviews_Survey/Survey_Analysis.xlsx
+++ b/Interviews_Survey/Survey_Analysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Studium\X_Masterarbeit\Data\Master_Thesis\Interviews_Survey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFC2EB0B-1542-405F-A5B7-904BCE4CC8FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DB20B77-5CCF-4D15-9A39-C0C91DB0CDD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -51,9 +51,6 @@
     <t>Details</t>
   </si>
   <si>
-    <t>Academic/research (Chalk streams typology (Univ. Southampton); Hidroclim; Comisiones GIRH)</t>
-  </si>
-  <si>
     <t>Governmental institutions (Town of Camden (Maine); Environment Agency (Flow Detectors Project))</t>
   </si>
   <si>
@@ -133,6 +130,9 @@
   </si>
   <si>
     <t>2, 1, 1, 1</t>
+  </si>
+  <si>
+    <t>Academic/research (Chalk streams typology (Uni Southampton); Hidroclim; Comisiones GIRH)</t>
   </si>
 </sst>
 </file>
@@ -479,7 +479,7 @@
   <cols>
     <col min="1" max="1" width="24.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="91.6640625" customWidth="1"/>
+    <col min="3" max="3" width="139.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -494,7 +494,7 @@
         <v>7</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1"/>
     </row>
@@ -503,7 +503,7 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D2">
         <v>2</v>
@@ -514,7 +514,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D3">
         <v>6</v>
@@ -525,7 +525,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -536,7 +536,7 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -550,7 +550,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -569,7 +569,7 @@
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="D8">
         <v>3</v>
@@ -580,7 +580,7 @@
         <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -591,7 +591,7 @@
         <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -599,21 +599,21 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
         <v>11</v>
       </c>
-      <c r="C11" t="s">
-        <v>12</v>
-      </c>
       <c r="D11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D12">
         <v>4</v>
@@ -621,10 +621,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -632,40 +632,40 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
         <v>15</v>
       </c>
-      <c r="C15" t="s">
-        <v>16</v>
-      </c>
       <c r="D15">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D16">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D17">
         <v>2</v>
@@ -673,10 +673,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D18">
         <v>2</v>
@@ -684,10 +684,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" t="s">
         <v>20</v>
-      </c>
-      <c r="C19" t="s">
-        <v>21</v>
       </c>
       <c r="D19">
         <v>5</v>
@@ -695,10 +695,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D20">
         <v>10</v>
@@ -706,10 +706,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -717,21 +717,21 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D23">
         <v>5</v>
